--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486552_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486552_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4964</v>
+        <v>0.9396</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2605</v>
+        <v>2.9194</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7641</v>
+        <v>-1.9799</v>
       </c>
       <c r="G2" t="n">
         <v>0.0556</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1358</v>
+        <v>0.5789</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5502</v>
+        <v>0.2091</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5856</v>
+        <v>0.3698</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0045</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E3" t="n">
         <v>0.7628</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7672</v>
+        <v>-0.6748</v>
       </c>
       <c r="G3" t="n">
         <v>0.2763</v>
@@ -688,13 +688,13 @@
         <v>0.2175</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4983</v>
+        <v>-0.4059</v>
       </c>
       <c r="T3" t="n">
         <v>-0.4795</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0189</v>
+        <v>0.0736</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4391</v>
+        <v>-0.8415</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7111</v>
+        <v>0.3913</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1502</v>
+        <v>-1.2327</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.9184</v>
+        <v>-0.5109</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5845</v>
+        <v>-0.0822</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3339</v>
+        <v>-0.4287</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7166</v>
+        <v>0.604</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8696</v>
+        <v>0.5657</v>
       </c>
       <c r="L4" t="n">
-        <v>0.153</v>
+        <v>0.0382</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2018</v>
+        <v>-1.1149</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7149</v>
+        <v>-0.6479</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4869</v>
+        <v>-0.467</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5446</v>
+        <v>-0.5056</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0601</v>
+        <v>-0.2127</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4845</v>
+        <v>-0.2929</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9347</v>
+        <v>-1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5204</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. VAN OOSTRUM</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.293</v>
+        <v>-1.1327</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.9267</v>
+        <v>0.2641</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6337</v>
+        <v>-1.3967</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4265</v>
+        <v>-1.9184</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7512</v>
+        <v>-1.5845</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1778</v>
+        <v>-0.3339</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0824</v>
+        <v>-0.7166</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4348</v>
+        <v>-0.8696</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5172</v>
+        <v>0.153</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3442</v>
+        <v>-1.2018</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3164</v>
+        <v>-0.7149</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6606</v>
+        <v>-0.4869</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-2.3926</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.632</v>
+        <v>-0.149</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6165</v>
+        <v>-0.3869</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0155</v>
+        <v>0.2379</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9347</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>D. VAN OOSTRUM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3377</v>
+        <v>-1.2622</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0125</v>
+        <v>-2.9267</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3252</v>
+        <v>1.6645</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5109</v>
+        <v>0.4265</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0822</v>
+        <v>-0.7512</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4287</v>
+        <v>1.1778</v>
       </c>
       <c r="J6" t="n">
-        <v>0.604</v>
+        <v>0.0824</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5657</v>
+        <v>-0.4348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0382</v>
+        <v>0.5172</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1149</v>
+        <v>0.3442</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6479</v>
+        <v>-0.3164</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.467</v>
+        <v>0.6606</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R6" t="n">
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0019</v>
+        <v>-0.6011</v>
       </c>
       <c r="T6" t="n">
         <v>-0.6165</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3854</v>
+        <v>0.0153</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4862</v>
+        <v>-1.2742</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.4142</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7366</v>
+        <v>-0.8599</v>
       </c>
       <c r="G7" t="n">
         <v>0.1523</v>
@@ -1000,13 +1000,13 @@
         <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.7523</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2329</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2687</v>
+        <v>0.1454</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1093</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8899</v>
+        <v>-1.4167</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4268</v>
+        <v>1.0541</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3167</v>
+        <v>-2.4708</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8045</v>
@@ -1078,13 +1078,13 @@
         <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0653</v>
+        <v>-0.5921</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0959</v>
+        <v>-0.4687</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0306</v>
+        <v>-0.1235</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7602</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3157</v>
+        <v>-2.8581</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4945</v>
+        <v>0.6748</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.8102</v>
+        <v>-3.5328</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3807</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1525</v>
+        <v>-0.6949</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1454</v>
+        <v>0.0349</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0071</v>
+        <v>-0.7297</v>
       </c>
       <c r="V9" t="n">
         <v>-1.13</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4445</v>
+        <v>-5.5995</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.113</v>
+        <v>-4.2681</v>
       </c>
       <c r="F10" t="n">
         <v>-1.3315</v>
@@ -1234,10 +1234,10 @@
         <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.6585</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1454</v>
+        <v>-0.3004</v>
       </c>
       <c r="U10" t="n">
         <v>-0.3581</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6427</v>
+        <v>-6.2582</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.8501</v>
+        <v>-6.5581</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2074</v>
+        <v>0.2999</v>
       </c>
       <c r="G11" t="n">
         <v>-4.3352</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1749</v>
+        <v>-0.7904</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0959</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.079</v>
+        <v>0.0135</v>
       </c>
       <c r="V11" t="n">
         <v>1.695</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.1531</v>
+        <v>-8.5519</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.535</v>
+        <v>-6.088</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.618</v>
+        <v>-2.4639</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7503</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6627</v>
+        <v>-0.0616</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6165</v>
+        <v>-0.1694</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0463</v>
+        <v>0.1078</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2599</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-28.51</v>
+        <v>-28.1674</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.5311</v>
+        <v>-14.1886</v>
       </c>
       <c r="F13" t="n">
         <v>-13.9786</v>
@@ -1441,10 +1441,10 @@
         <v>-2.9803</v>
       </c>
       <c r="J13" t="n">
-        <v>6.722699999999998</v>
+        <v>6.7227</v>
       </c>
       <c r="K13" t="n">
-        <v>2.921300000000001</v>
+        <v>2.9213</v>
       </c>
       <c r="L13" t="n">
         <v>3.8011</v>
@@ -1468,13 +1468,13 @@
         <v>15.2254</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.974899999999999</v>
+        <v>-4.6325</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.434200000000001</v>
+        <v>-4.0917</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5409000000000003</v>
+        <v>-0.5408999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-5.6499</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1405</v>
+        <v>6.0668</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2592</v>
+        <v>3.9509</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8812</v>
+        <v>2.1159</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8641</v>
+        <v>2.9568</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5517</v>
+        <v>1.2714</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3124</v>
+        <v>1.6853</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6819</v>
+        <v>3.0485</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2666</v>
+        <v>1.1743</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4152</v>
+        <v>1.8742</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8178</v>
+        <v>-0.0917</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7149</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1029</v>
+        <v>-0.1889</v>
       </c>
       <c r="P14" t="n">
-        <v>1.305</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2111</v>
+        <v>0.2851</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9047</v>
+        <v>-0.3124</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3064</v>
+        <v>0.5975</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7602</v>
+        <v>2.8249</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7602</v>
+        <v>3.3899</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8741</v>
+        <v>5.7994</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7274</v>
+        <v>4.9181</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1467</v>
+        <v>0.8812</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9568</v>
+        <v>2.8641</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2714</v>
+        <v>2.5517</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6853</v>
+        <v>0.3124</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0485</v>
+        <v>4.6819</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1743</v>
+        <v>3.2666</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8742</v>
+        <v>1.4152</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0917</v>
+        <v>-1.8178</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.7149</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1889</v>
+        <v>-1.1029</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>1.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0924</v>
+        <v>0.87</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.536</v>
+        <v>0.5636</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6284</v>
+        <v>0.3064</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8249</v>
+        <v>0.7602</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3899</v>
+        <v>0.7602</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8021</v>
+        <v>4.095</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6812</v>
+        <v>2.1282</v>
       </c>
       <c r="F16" t="n">
-        <v>2.121</v>
+        <v>1.9669</v>
       </c>
       <c r="G16" t="n">
         <v>1.0639</v>
@@ -1702,13 +1702,13 @@
         <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2157</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6044</v>
+        <v>-0.1574</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.666</v>
       </c>
       <c r="V16" t="n">
         <v>0.5649999999999999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9067</v>
+        <v>3.1533</v>
       </c>
       <c r="E17" t="n">
         <v>1.8378</v>
       </c>
       <c r="F17" t="n">
-        <v>1.069</v>
+        <v>1.3155</v>
       </c>
       <c r="G17" t="n">
         <v>3.826</v>
@@ -1780,13 +1780,13 @@
         <v>2.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4059</v>
+        <v>0.6525</v>
       </c>
       <c r="T17" t="n">
         <v>0.4266</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0207</v>
+        <v>0.2259</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3252</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>A. HOLDER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6646</v>
+        <v>2.6399</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4853</v>
+        <v>1.2465</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1793</v>
+        <v>1.3933</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3148</v>
+        <v>-0.4656</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8455</v>
+        <v>-0.3406</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4693</v>
+        <v>-0.1251</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4186</v>
+        <v>-0.3142</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0799</v>
+        <v>-0.1246</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3387</v>
+        <v>-0.1896</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1038</v>
+        <v>-0.1514</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2344</v>
+        <v>-0.216</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8694</v>
+        <v>0.0645</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5466</v>
+        <v>0.0403</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0911</v>
+        <v>0.2355</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4554</v>
+        <v>-0.1953</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0207</v>
+        <v>1.3252</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1507</v>
+        <v>1.3252</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. HOLDER</t>
+          <t>A. BARCELLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3547</v>
+        <v>2.517</v>
       </c>
       <c r="E19" t="n">
-        <v>1.023</v>
+        <v>2.1121</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3317</v>
+        <v>0.405</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4656</v>
+        <v>0.8857</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3406</v>
+        <v>1.536</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1251</v>
+        <v>-0.6502</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3142</v>
+        <v>2.4365</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1246</v>
+        <v>1.9193</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1896</v>
+        <v>0.5172</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1514</v>
+        <v>-1.5508</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.216</v>
+        <v>-0.3834</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0645</v>
+        <v>-1.1674</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2449</v>
+        <v>0.3263</v>
       </c>
       <c r="T19" t="n">
-        <v>0.012</v>
+        <v>-0.3245</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2569</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BARCELLO</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1086</v>
+        <v>1.9941</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8886</v>
+        <v>1.8148</v>
       </c>
       <c r="F20" t="n">
-        <v>0.22</v>
+        <v>0.1793</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8857</v>
+        <v>1.3148</v>
       </c>
       <c r="H20" t="n">
-        <v>1.536</v>
+        <v>0.8455</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6502</v>
+        <v>0.4693</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4365</v>
+        <v>2.4186</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9193</v>
+        <v>1.0799</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5172</v>
+        <v>1.3387</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5508</v>
+        <v>-1.1038</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3834</v>
+        <v>-0.2344</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1674</v>
+        <v>-0.8694</v>
       </c>
       <c r="P20" t="n">
-        <v>1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0822</v>
+        <v>0.876</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.548</v>
+        <v>0.4206</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4658</v>
+        <v>0.4554</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.0207</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1507</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.009</v>
+        <v>1.8713</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2692</v>
+        <v>-1.6661</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2782</v>
+        <v>3.5373</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.265</v>
+        <v>-0.6021</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8331</v>
+        <v>-0.1854</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5681</v>
+        <v>-0.4168</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-1.6204</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6657</v>
+        <v>-0.6475</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0765</v>
+        <v>-0.9729</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3242</v>
+        <v>1.0183</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1674</v>
+        <v>0.4621</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4916</v>
+        <v>0.5562</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>0.709</v>
+        <v>0.5158</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2776</v>
+        <v>-0.0457</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4314</v>
+        <v>0.5615</v>
       </c>
       <c r="V21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.7132</v>
+        <v>1.6737</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2249</v>
+        <v>-0.6045</v>
       </c>
       <c r="F22" t="n">
-        <v>3.938</v>
+        <v>2.2782</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6021</v>
+        <v>-0.265</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1854</v>
+        <v>-0.8331</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4168</v>
+        <v>0.5681</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6204</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6475</v>
+        <v>-0.6657</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9729</v>
+        <v>0.0765</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0183</v>
+        <v>0.3242</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4621</v>
+        <v>-0.1674</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5562</v>
+        <v>0.4916</v>
       </c>
       <c r="P22" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3577</v>
+        <v>0.3737</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6044</v>
+        <v>-0.0577</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.4314</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1543</v>
+        <v>0.4774</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0445</v>
+        <v>-0.0131</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1098</v>
+        <v>0.4906</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.452</v>
+        <v>1.4591</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.146</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.306</v>
+        <v>0.6622</v>
       </c>
       <c r="J23" t="n">
-        <v>0.113</v>
+        <v>3.1589</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0365</v>
+        <v>1.6274</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0765</v>
+        <v>1.5316</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.6998</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1825</v>
+        <v>-0.8304</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3825</v>
+        <v>-0.8694</v>
       </c>
       <c r="P23" t="n">
-        <v>0.87</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R23" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.4984</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0481</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.4503</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1237</v>
+        <v>0.2661</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4602</v>
+        <v>0.1563</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3365</v>
+        <v>0.1098</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4591</v>
+        <v>-0.452</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7969000000000001</v>
+        <v>-0.146</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6622</v>
+        <v>-0.306</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1589</v>
+        <v>0.113</v>
       </c>
       <c r="K24" t="n">
-        <v>1.6274</v>
+        <v>0.0365</v>
       </c>
       <c r="L24" t="n">
-        <v>1.5316</v>
+        <v>0.0765</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6998</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8304</v>
+        <v>-0.1825</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8694</v>
+        <v>-0.3825</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.6101</v>
+        <v>0.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1027</v>
+        <v>0.0433</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.399</v>
+        <v>0.0433</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2962</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0941</v>
+        <v>-2.044</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.014</v>
+        <v>-1.9023</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0801</v>
+        <v>-0.1417</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2258</v>
@@ -2404,13 +2404,13 @@
         <v>1.9576</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.015</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3458</v>
+        <v>0.2842</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5857</v>
@@ -2449,7 +2449,7 @@
         <v>11.3599</v>
       </c>
       <c r="H26" t="n">
-        <v>8.379500000000002</v>
+        <v>8.3795</v>
       </c>
       <c r="I26" t="n">
         <v>2.9802</v>
@@ -2470,10 +2470,10 @@
         <v>-2.9215</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.8013</v>
+        <v>-3.801299999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>6.525199999999998</v>
+        <v>6.525199999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-15.2255</v>
@@ -2485,13 +2485,13 @@
         <v>4.975000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5407</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>4.4341</v>
+        <v>4.434000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>5.649899999999999</v>
+        <v>5.6499</v>
       </c>
       <c r="W26" t="n">
         <v>10.581</v>
